--- a/转录数据/LLM转录.xlsx
+++ b/转录数据/LLM转录.xlsx
@@ -830,8 +830,14 @@
       <c r="D14" t="str">
         <v>名词</v>
       </c>
+      <c r="E14" t="str">
+        <v>人</v>
+      </c>
       <c r="F14" t="str">
         <v>个</v>
+      </c>
+      <c r="G14" t="str">
+        <v>普通词</v>
       </c>
       <c r="H14" t="str">
         <v>普通量词</v>
